--- a/documentacion/WPL/4-WPL-dedication.xlsx
+++ b/documentacion/WPL/4-WPL-dedication.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Javie\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Javie\Desktop\UNIVERSIDAD\ISPP\entregas\WPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F419D7-FEB6-469F-BF3B-2D8E9E9A9413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE7852C-4590-4746-A7BE-D4F5798A3625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{02C8C9D8-2F21-45BA-9A66-91BB45160C54}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
   <si>
     <t>Nombre</t>
   </si>
@@ -164,6 +164,9 @@
   </si>
   <si>
     <t>Comentarios sobre DP</t>
+  </si>
+  <si>
+    <t>World project launch (#WPL)</t>
   </si>
 </sst>
 </file>
@@ -296,10 +299,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -731,7 +734,7 @@
     <col min="3" max="7" width="10.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="5" customFormat="1" ht="48" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="5" customFormat="1" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -753,8 +756,11 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H1" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -776,8 +782,11 @@
       <c r="G2" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -799,8 +808,11 @@
       <c r="G3" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H3" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -822,8 +834,11 @@
       <c r="G4" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -845,8 +860,11 @@
       <c r="G5" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -868,8 +886,11 @@
       <c r="G6" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -891,8 +912,11 @@
       <c r="G7" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -914,9 +938,12 @@
       <c r="G8" s="3">
         <v>1</v>
       </c>
-      <c r="I8" s="12"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="I8" s="11"/>
+    </row>
+    <row r="9" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -938,8 +965,11 @@
       <c r="G9" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
@@ -961,8 +991,11 @@
       <c r="G10" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>24</v>
       </c>
@@ -984,8 +1017,11 @@
       <c r="G11" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>26</v>
       </c>
@@ -1007,8 +1043,11 @@
       <c r="G12" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>28</v>
       </c>
@@ -1030,8 +1069,11 @@
       <c r="G13" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="H13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>30</v>
       </c>
@@ -1051,6 +1093,9 @@
         <v>1</v>
       </c>
       <c r="G14" s="3">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1063,7 +1108,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1087,8 +1132,12 @@
         <f>SUM(G2:G14)/$B$16</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H17" s="6">
+        <f>SUM(H2:H14)/$B$16</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -1112,8 +1161,12 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18" s="7">
+        <f t="shared" ref="H18" si="1">1-H17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>35</v>
       </c>
@@ -1121,37 +1174,37 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="11" t="s">
+    <row r="22" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-    </row>
-    <row r="23" spans="1:7" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="11" t="s">
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+    </row>
+    <row r="23" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-    </row>
-    <row r="24" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="11" t="s">
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+    </row>
+    <row r="24" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-    </row>
-    <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+    </row>
+    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D27" s="9"/>
     </row>
   </sheetData>
@@ -1160,7 +1213,7 @@
     <mergeCell ref="B23:G23"/>
     <mergeCell ref="B24:G24"/>
   </mergeCells>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C17:H17">
     <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>1</formula>
     </cfRule>
@@ -1174,7 +1227,7 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C18:H18">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>""</formula>
     </cfRule>
@@ -1245,15 +1298,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8ec00d9b-94f7-475a-85dc-f517f90086c9">
@@ -1262,6 +1306,15 @@
     <TaxCatchAll xmlns="b7f08318-9e67-4cf6-83a6-3e1ba6c01486" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1454,20 +1507,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F4B272D-551A-4AF9-B220-C688C9745ED1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D0D844A-E87E-42E2-B155-132CABE67861}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="8ec00d9b-94f7-475a-85dc-f517f90086c9"/>
     <ds:schemaRef ds:uri="b7f08318-9e67-4cf6-83a6-3e1ba6c01486"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F4B272D-551A-4AF9-B220-C688C9745ED1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
